--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440376.5654321911</v>
+        <v>440377</v>
       </c>
       <c r="R2" t="n">
-        <v>6951877.836387456</v>
+        <v>6951878</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1965-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20135-2025 artfynd.xlsx
+++ b/artfynd/A 20135-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686987</v>
       </c>
       <c r="B2" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
